--- a/01_プロジェクト/BUYMA購入者配布資料/BUYMA_出品管理表_購入者版.xlsx
+++ b/01_プロジェクト/BUYMA購入者配布資料/BUYMA_出品管理表_購入者版.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出品管理" sheetId="1" r:id="Re248a2e1e2014e98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="2" r:id="Reb5c52626e4b48f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="3" r:id="R17a638dfcc3646c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関税・分類確認" sheetId="4" r:id="R872df3bc1bac48c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出品管理" sheetId="1" r:id="R7b21f6b8be354c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="2" r:id="Re528312cc5b44ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="3" r:id="R975db867e8e345f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関税・分類確認" sheetId="4" r:id="R7a28afaa27ba45ec"/>
   </x:sheets>
 </x:workbook>
 </file>
